--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="1470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="1478">
   <si>
     <t>Facebook</t>
   </si>
@@ -5489,6 +5489,37 @@
       </rPr>
       <t>每個角色、場景和技能效果都呈現出極具創意和魅力的點數藝術，讓你在回憶經典的同時，享受全新的遊戲體驗。</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>浣熊傳說</t>
+  </si>
+  <si>
+    <t>勇者格鬥城</t>
+  </si>
+  <si>
+    <t>6500鑽石</t>
+  </si>
+  <si>
+    <t>6200鑽石</t>
+  </si>
+  <si>
+    <t>1680鑽石</t>
+  </si>
+  <si>
+    <t>880鑽石</t>
+  </si>
+  <si>
+    <t>即時高智商對戰！獨創五行制衡戰術！
+過百種浣熊英雄！每張都是藝術品！
+全球PVP競技場！用策略證明誰是浣熊之王！
+無門檻終極狂歡！首發限定SSR免費領！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《勇者格鬥城》橫版動作手遊震撼來襲！六大職業任選，暢爽連招對決BOSS。挑戰深淵副本贏稀有裝備，PVP競技場展現操作實力。無論是冒險獨行俠還是競技達人，都能找到專屬戰鬥樂趣！即刻加入，體驗極致打擊快感，爭奪最強勇者稱號！
+【六大獨特職業】
+任你選擇，專屬技能與戰鬥風格帶來截然不同的體驗！挑戰多層次副本，從普通地下城到深淵Boss，海量關卡，驚喜不斷！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -19225,7 +19256,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F163" si="3">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F165" si="3">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="24" t="s">
@@ -19400,8 +19431,174 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="29" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F164" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=浣熊傳說</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="5">
+        <v>2327</v>
+      </c>
+      <c r="K164" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L164" s="5">
+        <v>1160</v>
+      </c>
+      <c r="M164" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N164" s="5">
+        <v>771</v>
+      </c>
+      <c r="O164" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P164" s="5">
+        <v>529</v>
+      </c>
+      <c r="Q164" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="R164" s="5">
+        <v>260</v>
+      </c>
+      <c r="S164" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T164" s="5">
+        <v>143</v>
+      </c>
+      <c r="U164" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="V164" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="29" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F165" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=勇者格鬥城</v>
+      </c>
+      <c r="H165" s="6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="J165" s="5">
+        <v>2494</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L165" s="5">
+        <v>2413</v>
+      </c>
+      <c r="M165" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N165" s="5">
+        <v>1946</v>
+      </c>
+      <c r="O165" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P165" s="5">
+        <v>1276</v>
+      </c>
+      <c r="Q165" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R165" s="5">
+        <v>1167</v>
+      </c>
+      <c r="S165" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T165" s="5">
+        <v>771</v>
+      </c>
+      <c r="U165" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="V165" s="5">
+        <v>654</v>
+      </c>
+      <c r="W165" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="X165" s="5">
+        <v>505</v>
+      </c>
+      <c r="Y165" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z165" s="5">
+        <v>387</v>
+      </c>
+      <c r="AA165" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="AB165" s="5">
+        <v>347</v>
+      </c>
+      <c r="AC165" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD165" s="5">
+        <v>268</v>
+      </c>
+      <c r="AE165" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AF165" s="5">
+        <v>160</v>
+      </c>
+      <c r="AG165" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH165" s="5">
+        <v>126</v>
+      </c>
+      <c r="AI165" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="AJ165" s="5">
+        <v>118</v>
+      </c>
+      <c r="AK165" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL165" s="5">
+        <v>76</v>
+      </c>
+      <c r="AM165" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="AN165" s="5">
+        <v>50</v>
+      </c>
+      <c r="AO165" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP165" s="5">
+        <v>25</v>
+      </c>
+    </row>
     <row r="166" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="167" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="168" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="1478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="1501">
   <si>
     <t>Facebook</t>
   </si>
@@ -5521,6 +5521,81 @@
 【六大獨特職業】
 任你選擇，專屬技能與戰鬥風格帶來截然不同的體驗！挑戰多層次副本，從普通地下城到深淵Boss，海量關卡，驚喜不斷！</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龐寶：背包英雄們</t>
+  </si>
+  <si>
+    <t>星耀球會</t>
+  </si>
+  <si>
+    <t>背上小小背包出發世界旅行的白熊, 龐寶。偶然遇見的寶箱怪低著聲說「從你身上感受到勇士的氣息。」
+一直沉睡的魔像“領路者”醒了過來,龐寶則和36位夥伴一起向著新大陸前進。而那個地方有著可怕的魔王“藍波”在等著。
+“現在, 是時候由背著背包的命運勇士 - 龐寶照亮前方的路了。”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《星耀球會》一款由球隊名、隊徽、主場風格任你設計的手遊，玩家將同時化身事會主席、球探、經理、甚至教練。你的球會，由你話事!
+遊戲以「球會」為核心，玩家唔止係揀陣式咁簡單。由起訓練設施、規劃財政、球員買賣、隊伍發展，到球場設計都由你話事。你係球會掌舵人，完全掌控整個球會並自己心目中的理想！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100鑽石</t>
+  </si>
+  <si>
+    <t>250鑽石</t>
+  </si>
+  <si>
+    <t>去除廣告禮包</t>
+  </si>
+  <si>
+    <t>10800金幣</t>
+  </si>
+  <si>
+    <t>5000金幣</t>
+  </si>
+  <si>
+    <t>1700金幣</t>
+  </si>
+  <si>
+    <t>800金幣</t>
+  </si>
+  <si>
+    <t>380金幣</t>
+  </si>
+  <si>
+    <t>150金幣</t>
+  </si>
+  <si>
+    <t>東方幻想ECLIPSE</t>
+  </si>
+  <si>
+    <t>被遺忘之人匯聚的樂園——幻想鄉。 人類與妖怪在這片寧靜之地共存，歲月靜好，彷彿永恆不變…… 然而，突如其來的「它們」，打破了這份安寧。 前所未見的異質存在，如暗潮般悄然蔓延，將整個幻想鄉捲入前所未有的混亂。 生活在這片土地上的「她們」，懷抱著各自的信念與使命，踏上了行動的旅途。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16450幻晶石</t>
+  </si>
+  <si>
+    <t>8450幻晶石</t>
+  </si>
+  <si>
+    <t>4950幻晶石</t>
+  </si>
+  <si>
+    <t>2450幻晶石</t>
+  </si>
+  <si>
+    <t>850幻晶石</t>
+  </si>
+  <si>
+    <t>165幻晶石</t>
+  </si>
+  <si>
+    <t>490台幣禮包</t>
+  </si>
+  <si>
+    <t>250台幣禮包</t>
   </si>
 </sst>
 </file>
@@ -5665,7 +5740,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5754,6 +5829,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -19256,7 +19333,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F165" si="3">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F174" si="3">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="24" t="s">
@@ -19599,9 +19676,216 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="29" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F166" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=龐寶：背包英雄們</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>1480</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J166" s="5">
+        <v>2335</v>
+      </c>
+      <c r="K166" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L166" s="5">
+        <v>1284</v>
+      </c>
+      <c r="M166" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N166" s="5">
+        <v>521</v>
+      </c>
+      <c r="O166" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="P166" s="5">
+        <v>260</v>
+      </c>
+      <c r="Q166" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="R166" s="5">
+        <v>139</v>
+      </c>
+      <c r="S166" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="T166" s="5">
+        <v>83</v>
+      </c>
+      <c r="U166" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="V166" s="5">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="167" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="29" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F167" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=星耀球會</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>1481</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>1485</v>
+      </c>
+      <c r="J167" s="5">
+        <v>2296</v>
+      </c>
+      <c r="K167" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L167" s="5">
+        <v>1144</v>
+      </c>
+      <c r="M167" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="N167" s="5">
+        <v>529</v>
+      </c>
+      <c r="O167" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="P167" s="5">
+        <v>260</v>
+      </c>
+      <c r="Q167" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="R167" s="5">
+        <v>143</v>
+      </c>
+      <c r="S167" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="T167" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="168" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="30" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F168" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=東方幻想ECLIPSE</v>
+      </c>
+      <c r="H168" s="31" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J168" s="5">
+        <v>2539</v>
+      </c>
+      <c r="K168" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="L168" s="5">
+        <v>1323</v>
+      </c>
+      <c r="M168" s="4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="N168" s="5">
+        <v>775</v>
+      </c>
+      <c r="O168" s="4" t="s">
+        <v>1496</v>
+      </c>
+      <c r="P168" s="5">
+        <v>389</v>
+      </c>
+      <c r="Q168" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="R168" s="5">
+        <v>144</v>
+      </c>
+      <c r="S168" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="T168" s="5">
+        <v>28</v>
+      </c>
+      <c r="U168" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="V168" s="5">
+        <v>2539</v>
+      </c>
+      <c r="W168" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="X168" s="5">
+        <v>1558</v>
+      </c>
+      <c r="Y168" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z168" s="5">
+        <v>1323</v>
+      </c>
+      <c r="AA168" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB168" s="5">
+        <v>1010</v>
+      </c>
+      <c r="AC168" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="AD168" s="5">
+        <v>775</v>
+      </c>
+      <c r="AE168" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AF168" s="5">
+        <v>389</v>
+      </c>
+      <c r="AG168" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="AH168" s="5">
+        <v>262</v>
+      </c>
+      <c r="AI168" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AJ168" s="5">
+        <v>198</v>
+      </c>
+      <c r="AK168" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL168" s="5">
+        <v>144</v>
+      </c>
+      <c r="AM168" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="AN168" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="169" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="170" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="171" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="1501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1521">
   <si>
     <t>Facebook</t>
   </si>
@@ -5597,12 +5597,103 @@
   <si>
     <t>250台幣禮包</t>
   </si>
+  <si>
+    <t>世紀帝國M</t>
+  </si>
+  <si>
+    <t>歐啦!守得豬</t>
+  </si>
+  <si>
+    <t>18櫻花幕府</t>
+  </si>
+  <si>
+    <t>50000帝國幣</t>
+  </si>
+  <si>
+    <t>24000帝國幣</t>
+  </si>
+  <si>
+    <t>9200帝國幣</t>
+  </si>
+  <si>
+    <r>
+      <t>4400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>帝國幣</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100帝國幣</t>
+  </si>
+  <si>
+    <t>400帝國幣</t>
+  </si>
+  <si>
+    <r>
+      <t>1320</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>鑽石</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《世紀帝國M》引入玩家熟悉的八大文明(中式、羅馬式、法蘭克式、拜占庭式、埃及式、不列顛式、日式及韓式)、傭兵系統，以及經典的資源採集和分配機制，玩家需要合理安排村民進行採礦、捕魚、打獵、採樹莓…等，收集、累積、分配資源用於發展帝國；此外，《世紀帝國》經典的音樂音效、宏偉逼真的攻城器械也將在遊戲中出現，玩家不僅能使用到豐富的策略，更能被喚起有關《世紀帝國》的美好回憶。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>誰說英雄一定要帥？《歐啦！守得豬》的英雄角色可謂是「跨次元」的明星大集合！我們汲取了大量流行元素，巧妙地將其與各種動物形象融合，打造出個性十足、醜萌兼具的天團戰隊。每一位英雄都身懷絕技，每一次召喚都可能帶來意外的驚喜與強大的戰力。各種趣味屬性、羈絆配搭，讓策略變得既豐富又有趣，誰說塔防一定嚴肅？來點萌萌鬼畜，笑著守住你的家園！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰姬的魅力，從不只在戰場！每位乙女皆擁有隱藏立繪與進階服裝，隨著升星、親密互動、羈絆突破逐步解鎖---從威武戰甲到柔情私服，從冷豔武將到嬌羞美人。這場亂世，不只是爭霸，更是攻略每一顆芳心。
+《18櫻花幕府》與盟友並肩奪城，成為一國之主！
+加入家族，參與大型跨服城戰。運籌帷幄，調度戰姬，佔領據點、掠奪資源，證明你才是真正的幕府霸主。兄弟齊心，其利斷金，稱霸戰國等你來挑戰！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000代金券</t>
+  </si>
+  <si>
+    <t>5000代金券</t>
+  </si>
+  <si>
+    <t>3000代金券</t>
+  </si>
+  <si>
+    <t>2000代金券</t>
+  </si>
+  <si>
+    <t>1000代金券</t>
+  </si>
+  <si>
+    <t>500代金券</t>
+  </si>
+  <si>
+    <t>100代金券</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5660,6 +5751,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
@@ -19886,9 +19984,168 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="29" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F169" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=世紀帝國M</v>
+      </c>
+      <c r="H169" s="31" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="J169" s="5">
+        <v>2508</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="L169" s="5">
+        <v>1268</v>
+      </c>
+      <c r="M169" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="N169" s="5">
+        <v>548</v>
+      </c>
+      <c r="O169" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="P169" s="5">
+        <v>278</v>
+      </c>
+      <c r="Q169" s="4" t="s">
+        <v>1508</v>
+      </c>
+      <c r="R169" s="5">
+        <v>127</v>
+      </c>
+      <c r="S169" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="T169" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="29" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F170" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=歐啦!守得豬</v>
+      </c>
+      <c r="H170" s="31" t="s">
+        <v>1512</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J170" s="5">
+        <v>2539</v>
+      </c>
+      <c r="K170" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L170" s="5">
+        <v>1323</v>
+      </c>
+      <c r="M170" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="N170" s="5">
+        <v>579</v>
+      </c>
+      <c r="O170" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="P170" s="5">
+        <v>294</v>
+      </c>
+      <c r="Q170" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R170" s="5">
+        <v>144</v>
+      </c>
+      <c r="S170" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="T170" s="5">
+        <v>28</v>
+      </c>
+      <c r="U170" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="V170" s="5">
+        <v>294</v>
+      </c>
+      <c r="W170" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="X170" s="5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="171" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="29" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F171" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=18櫻花幕府</v>
+      </c>
+      <c r="H171" s="6" t="s">
+        <v>1513</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J171" s="5">
+        <v>2340</v>
+      </c>
+      <c r="K171" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="L171" s="5">
+        <v>1166</v>
+      </c>
+      <c r="M171" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="N171" s="5">
+        <v>775</v>
+      </c>
+      <c r="O171" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="P171" s="5">
+        <v>532</v>
+      </c>
+      <c r="Q171" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="R171" s="5">
+        <v>262</v>
+      </c>
+      <c r="S171" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="T171" s="5">
+        <v>144</v>
+      </c>
+      <c r="U171" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="V171" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="172" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="173" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="174" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1529">
   <si>
     <t>Facebook</t>
   </si>
@@ -5687,6 +5687,33 @@
   </si>
   <si>
     <t>100代金券</t>
+  </si>
+  <si>
+    <t>大武道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
+遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6480仙玉</t>
+  </si>
+  <si>
+    <t>3280仙玉</t>
+  </si>
+  <si>
+    <t>1280仙玉</t>
+  </si>
+  <si>
+    <t>980仙玉</t>
+  </si>
+  <si>
+    <t>60仙玉</t>
+  </si>
+  <si>
+    <t>終身卡</t>
   </si>
 </sst>
 </file>
@@ -5838,7 +5865,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5929,6 +5956,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -19431,7 +19461,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F174" si="3">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F172" si="3">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="24" t="s">
@@ -20146,7 +20176,72 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="32" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F172" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=大武道</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J172" s="5">
+        <v>2539</v>
+      </c>
+      <c r="K172" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L172" s="5">
+        <v>1323</v>
+      </c>
+      <c r="M172" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="N172" s="5">
+        <v>532</v>
+      </c>
+      <c r="O172" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="P172" s="5">
+        <v>389</v>
+      </c>
+      <c r="Q172" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="R172" s="5">
+        <v>144</v>
+      </c>
+      <c r="S172" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="T172" s="5">
+        <v>28</v>
+      </c>
+      <c r="U172" s="4" t="s">
+        <v>1528</v>
+      </c>
+      <c r="V172" s="5">
+        <v>681</v>
+      </c>
+      <c r="W172" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="X172" s="5">
+        <v>144</v>
+      </c>
+      <c r="Y172" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z172" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="173" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="174" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="175" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1537">
   <si>
     <t>Facebook</t>
   </si>
@@ -5693,27 +5693,175 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>6480仙玉</t>
+  </si>
+  <si>
+    <t>3280仙玉</t>
+  </si>
+  <si>
+    <t>1280仙玉</t>
+  </si>
+  <si>
+    <t>980仙玉</t>
+  </si>
+  <si>
+    <t>60仙玉</t>
+  </si>
+  <si>
+    <t>終身卡</t>
+  </si>
+  <si>
+    <t>1650台幣商品</t>
+  </si>
+  <si>
+    <t>790台幣商品</t>
+  </si>
+  <si>
+    <t>690台幣商品</t>
+  </si>
+  <si>
+    <t>220台幣商品</t>
+  </si>
+  <si>
+    <t>190台幣商品</t>
+  </si>
+  <si>
+    <t>165台幣商品</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：爆走之翼</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：爆走之翼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是一款承襲經典</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>線上遊戲精髓的全新手機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MMORPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。它將熟悉的角色、華麗的裝備與技能完美移植到行動平台，讓玩家能隨時隨地回味奇蹟世界的感動。
+遊戲主打暢快的戰鬥節奏與豐富的副本挑戰，無論是單人闖關或組隊刷寶，都能體驗到爆棚的打擊感與策略樂趣。自動掛機系統讓玩家輕鬆升級，省下練功時間。此外，特色玩法如自由市場交易、翅膀養成、以及多樣化的競技模式，都將帶給玩家不同以往的奇蹟新體驗。立即下載《奇蹟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：爆走之翼》，重溫熱血傳說，再創輝煌！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
 遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6480仙玉</t>
-  </si>
-  <si>
-    <t>3280仙玉</t>
-  </si>
-  <si>
-    <t>1280仙玉</t>
-  </si>
-  <si>
-    <t>980仙玉</t>
-  </si>
-  <si>
-    <t>60仙玉</t>
-  </si>
-  <si>
-    <t>終身卡</t>
   </si>
 </sst>
 </file>
@@ -19461,7 +19609,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F172" si="3">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F173" si="3">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="24" t="s">
@@ -20185,28 +20333,28 @@
         <v>gift-codes.html?game=大武道</v>
       </c>
       <c r="H172" s="6" t="s">
+        <v>1536</v>
+      </c>
+      <c r="I172" s="4" t="s">
         <v>1522</v>
-      </c>
-      <c r="I172" s="4" t="s">
-        <v>1523</v>
       </c>
       <c r="J172" s="5">
         <v>2539</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="L172" s="5">
         <v>1323</v>
       </c>
       <c r="M172" s="4" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="N172" s="5">
         <v>532</v>
       </c>
       <c r="O172" s="4" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="P172" s="5">
         <v>389</v>
@@ -20218,13 +20366,13 @@
         <v>144</v>
       </c>
       <c r="S172" s="4" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="T172" s="5">
         <v>28</v>
       </c>
       <c r="U172" s="4" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="V172" s="5">
         <v>681</v>
@@ -20242,7 +20390,78 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="30" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F173" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=奇蹟MU：爆走之翼</v>
+      </c>
+      <c r="H173" s="24" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J173" s="5">
+        <v>2525</v>
+      </c>
+      <c r="K173" s="4" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L173" s="5">
+        <v>1284</v>
+      </c>
+      <c r="M173" s="4" t="s">
+        <v>1529</v>
+      </c>
+      <c r="N173" s="5">
+        <v>624</v>
+      </c>
+      <c r="O173" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="P173" s="5">
+        <v>545</v>
+      </c>
+      <c r="Q173" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="R173" s="5">
+        <v>387</v>
+      </c>
+      <c r="S173" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="T173" s="5">
+        <v>260</v>
+      </c>
+      <c r="U173" s="4" t="s">
+        <v>1531</v>
+      </c>
+      <c r="V173" s="5">
+        <v>174</v>
+      </c>
+      <c r="W173" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="X173" s="5">
+        <v>160</v>
+      </c>
+      <c r="Y173" s="4" t="s">
+        <v>1533</v>
+      </c>
+      <c r="Z173" s="5">
+        <v>139</v>
+      </c>
+      <c r="AA173" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB173" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="174" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="175" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="176" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -5729,6 +5729,11 @@
     <t>165台幣商品</t>
   </si>
   <si>
+    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
+遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -5756,14 +5761,14 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>：爆走之翼</t>
+      <t>：暴走之翼</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
@@ -5772,7 +5777,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -5780,16 +5785,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>：爆走之翼</t>
+      <t>：暴走之翼</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -5797,7 +5802,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
@@ -5806,7 +5811,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -5814,7 +5819,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
@@ -5823,7 +5828,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -5831,7 +5836,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
@@ -5841,7 +5846,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -5849,18 +5854,13 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>：爆走之翼》，重溫熱血傳說，再創輝煌！</t>
+      <t>：暴走之翼》，重溫熱血傳說，再創輝煌！</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《大武道》是一款將策略元素與武俠題材完美結合的國風卡牌遊戲。玩家將置身於一個充滿江湖恩怨的武俠世界，透過收集並培養各路經典武俠人物，組建專屬的強大隊伍。
-遊戲核心玩法在於其獨特的策略性卡牌對戰。你需要善用不同角色的技能搭配、陣營加成以及戰術佈局，才能在變幻莫測的戰場中克敵制勝。無論是PVE闖關還是PVP競技，每一次對決都是對你智慧的考驗。立即進入《大武道》，體驗最純粹的武俠策略樂趣，成就你的武林傳奇！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5868,7 +5868,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5933,6 +5933,17 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
@@ -6013,7 +6024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6106,6 +6117,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -20333,7 +20347,7 @@
         <v>gift-codes.html?game=大武道</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="I172" s="4" t="s">
         <v>1522</v>
@@ -20392,14 +20406,14 @@
     </row>
     <row r="173" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="30" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="F173" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>gift-codes.html?game=奇蹟MU：爆走之翼</v>
-      </c>
-      <c r="H173" s="24" t="s">
-        <v>1535</v>
+        <v>gift-codes.html?game=奇蹟MU：暴走之翼</v>
+      </c>
+      <c r="H173" s="33" t="s">
+        <v>1536</v>
       </c>
       <c r="I173" s="4" t="s">
         <v>156</v>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="1542">
   <si>
     <t>Facebook</t>
   </si>
@@ -5862,6 +5862,25 @@
       <t>：暴走之翼》，重溫熱血傳說，再創輝煌！</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《劍太傳說：新的開始》是一款東方武俠風格的MMORPG手遊，以精緻的畫面和廣闊的開放世界，邀請玩家踏入一個充滿傳奇的江湖。在遊戲中，你將扮演一位身懷絕技的武林人士，透過修煉各式武學、參與豐富的劇情任務，逐步揭開這片土地的秘密。遊戲提供多樣化的副本挑戰、緊張刺激的熱血幫戰以及考驗實力的跨服競技。為了您的遊戲體驗，我們也提供快速儲值服務，確保您能即時獲得所需資源，享受流暢的遊戲過程。立即加入《劍太傳說》，開啟你的專屬武俠傳奇，譜寫一個全新的江湖篇章！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《三國。群英燎原》是一款以經典三國歷史為背景的策略戰爭手遊。在這款遊戲中，玩家將穿越時空，化身一方霸主，親身體驗亂世之中爾虞我詐的權謀鬥爭。你的任務是招募並培養眾多耳熟能詳的三國傳奇武將，發展壯大自己的城池與勢力，並巧妙地調兵遣將，與其他玩家展開激烈的攻城掠地。遊戲的核心玩法著重於策略性的佈陣與即時戰鬥，搭配豐富的武將養成系統。我們提供安全儲值與正規儲值管道，讓您在擴張霸業的同時，能安心無虞地補充戰力。唯有深謀遠慮、知人善任，才能在這群雄割據的亂世中點燃燎原戰火，最終一統三國！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>劍太傳說：新的開始</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三國。群英燎原</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>終生特權</t>
   </si>
 </sst>
 </file>
@@ -19623,7 +19642,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F173" si="3">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F175" si="3">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="24" t="s">
@@ -20476,8 +20495,114 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="32" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F174" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=劍太傳說：新的開始</v>
+      </c>
+      <c r="H174" s="31" t="s">
+        <v>1537</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="J174" s="5">
+        <v>2539</v>
+      </c>
+      <c r="K174" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L174" s="5">
+        <v>1323</v>
+      </c>
+      <c r="M174" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="N174" s="5">
+        <v>775</v>
+      </c>
+      <c r="O174" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="P174" s="5">
+        <v>532</v>
+      </c>
+      <c r="Q174" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="R174" s="5">
+        <v>262</v>
+      </c>
+      <c r="S174" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="T174" s="5">
+        <v>144</v>
+      </c>
+      <c r="U174" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="V174" s="5">
+        <v>28</v>
+      </c>
+      <c r="W174" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="X174" s="5">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="175" spans="1:42" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="32" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F175" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>gift-codes.html?game=三國。群英燎原</v>
+      </c>
+      <c r="H175" s="31" t="s">
+        <v>1538</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="J175" s="5">
+        <v>2539</v>
+      </c>
+      <c r="K175" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L175" s="5">
+        <v>1323</v>
+      </c>
+      <c r="M175" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="N175" s="5">
+        <v>775</v>
+      </c>
+      <c r="O175" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="P175" s="5">
+        <v>262</v>
+      </c>
+      <c r="Q175" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="R175" s="5">
+        <v>144</v>
+      </c>
+      <c r="S175" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="T175" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="176" spans="1:42" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="178" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1560">
   <si>
     <t>Facebook</t>
   </si>
@@ -5885,6 +5885,85 @@
   <si>
     <t>canonical_url</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final War：寒霜前線</t>
+  </si>
+  <si>
+    <t>黑夜獵人</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Final War</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：寒霜前線》是一款引人入勝的末日冰雪主題策略生存手遊。在這個被冰雪覆蓋的嚴酷世界中，你將扮演指揮官，肩負著重建人類文明的重任。遊戲核心玩法融合了資源管理、基地建設與英雄養成，你需要抵抗酷寒、抵禦來襲的猛獸與敵對勢力。獨特的熔爐系統是維持溫暖與希望的關鍵。招募各具特色的英雄，搭配不同兵種，制定你的生存策略，並與全球玩家結盟或對抗。準備好在這場終極寒霜戰爭中，點燃文明的最後火種，帶領你的人民走向新生嗎？立即下載，體驗極致的生存挑戰與策略博弈！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《黑夜獵人：專治吸血鬼、殭屍與各種不服》是一款主打休閒塔防與策略對抗的哥德風手遊。你將化身為一名強大的吸血鬼獵人，在暗夜中佈下天羅地網，抵禦一波波來襲的殭屍、狼人與吸血鬼大軍。遊戲核心玩法是策略性地放置和升級你的防禦單位，結合英雄技能，消滅所有敵人。告別複雜操作，享受單手即可暢玩的割草快感與塔防樂趣。準備好運用你的智慧，建造最強防線，成為讓所有黑暗生物聞風喪膽的終極獵人了嗎？立即下載，體驗這場刺激又爽快的暗夜狩獵！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>別再讓老媽扛傷害了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>23000金幣</t>
+  </si>
+  <si>
+    <t>11200金幣</t>
+  </si>
+  <si>
+    <t>4400金幣</t>
+  </si>
+  <si>
+    <t>2200金幣</t>
+  </si>
+  <si>
+    <t>1000金幣</t>
+  </si>
+  <si>
+    <t>200金幣</t>
+  </si>
+  <si>
+    <t>7780紅寶石</t>
+  </si>
+  <si>
+    <t>3780紅寶石</t>
+  </si>
+  <si>
+    <t>1480紅寶石</t>
+  </si>
+  <si>
+    <t>750紅寶石</t>
+  </si>
+  <si>
+    <t>330紅寶石</t>
+  </si>
+  <si>
+    <t>60紅寶石</t>
   </si>
 </sst>
 </file>
@@ -6047,7 +6126,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6142,6 +6221,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6453,8 +6535,8 @@
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
-    <col min="2" max="3" width="5.25" style="1" customWidth="1"/>
-    <col min="4" max="5" width="5.25" style="2" customWidth="1"/>
+    <col min="2" max="3" width="14.625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="20" style="2" customWidth="1"/>
@@ -6464,7 +6546,7 @@
     <col min="40" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>328</v>
       </c>
@@ -8624,7 +8706,9 @@
         <f t="shared" si="1"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=英雄聯盟</v>
       </c>
-      <c r="I26" s="20"/>
+      <c r="I26" s="20" t="s">
+        <v>1547</v>
+      </c>
       <c r="J26" s="14" t="s">
         <v>579</v>
       </c>
@@ -17342,7 +17426,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H175" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H177" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20290,7 +20374,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F175" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F177" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -21307,23 +21391,125 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:43" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:43" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="29" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F176" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=Final War：寒霜前線</v>
+      </c>
+      <c r="H176" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=Final War：寒霜前線</v>
+      </c>
+      <c r="I176" s="24" t="s">
+        <v>1545</v>
+      </c>
+      <c r="J176" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="K176" s="5">
+        <v>2340</v>
+      </c>
+      <c r="L176" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="M176" s="5">
+        <v>1323</v>
+      </c>
+      <c r="N176" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="O176" s="5">
+        <v>532</v>
+      </c>
+      <c r="P176" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="Q176" s="5">
+        <v>262</v>
+      </c>
+      <c r="R176" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="S176" s="5">
+        <v>144</v>
+      </c>
+      <c r="T176" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="U176" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="29" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F177" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=黑夜獵人</v>
+      </c>
+      <c r="H177" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=黑夜獵人</v>
+      </c>
+      <c r="I177" s="34" t="s">
+        <v>1546</v>
+      </c>
+      <c r="J177" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="K177" s="5">
+        <v>2340</v>
+      </c>
+      <c r="L177" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="M177" s="5">
+        <v>1166</v>
+      </c>
+      <c r="N177" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="O177" s="5">
+        <v>548</v>
+      </c>
+      <c r="P177" s="4" t="s">
+        <v>1557</v>
+      </c>
+      <c r="Q177" s="5">
+        <v>254</v>
+      </c>
+      <c r="R177" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S177" s="5">
+        <v>127</v>
+      </c>
+      <c r="T177" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="U177" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="193" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="194" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="195" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1575">
   <si>
     <t>Facebook</t>
   </si>
@@ -5965,12 +5965,107 @@
   <si>
     <t>60紅寶石</t>
   </si>
+  <si>
+    <t>魔法黯道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>《魔法膽道》是一款闇黑像素風格的放置RPG手遊，帶你深入無盡地城展開刷寶冒險。新手上路務必尋找最新的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換豐富資源即可快人一步，輕鬆開荒。遊戲核心玩法是高度自由的配點與技能組合，讓你打造專屬流派。除了透過掛機農資源，許多玩家為了加速角色成長，會尋找專業的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務來獲取稀有道具與特權，讓戰力突飛猛進。無論是無課休閒玩家或課長，都能在這款遊戲中享受放置養成的樂趣，體驗復古又刺激的暗黑世界。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E9%AD%94%E6%B3%95%E9%BB%AF%E9%81%93/id6745922493</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/mfadofficial?fbclid=IwY2xjawL8GuRleHRuA2FlbQIxMABicmlkETFCWFVzVjJpdGw0WGZCQWZYAR4okRRMZdPKEN1G7OeiA1zHf3rr0itUlllP-XiC-ELD9696aXuCQos4a4woTg_aem_FiHf8qxIM1SQ8j2Bv67NQg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gamer.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/magicroadtw?locale=zh_TW</t>
+  </si>
+  <si>
+    <t>648代金鑽</t>
+  </si>
+  <si>
+    <t>328代金鑽</t>
+  </si>
+  <si>
+    <t>198代金鑽</t>
+  </si>
+  <si>
+    <t>128代金鑽</t>
+  </si>
+  <si>
+    <t>68代金鑽</t>
+  </si>
+  <si>
+    <t>30代金鑽</t>
+  </si>
+  <si>
+    <t>6代金鑽</t>
+  </si>
+  <si>
+    <t>免廣告卡</t>
+  </si>
+  <si>
+    <t>終生卡</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6050,6 +6145,15 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6126,7 +6230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6224,6 +6328,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17426,7 +17539,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H177" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H178" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20374,7 +20487,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F177" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F178" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -21443,7 +21556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="29" t="s">
         <v>1544</v>
       </c>
@@ -21495,21 +21608,108 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="35" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C178" s="37" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D178" s="36" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E178" s="36" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F178" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=魔法黯道</v>
+      </c>
+      <c r="G178" s="36" t="s">
+        <v>1564</v>
+      </c>
+      <c r="H178" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=魔法黯道</v>
+      </c>
+      <c r="I178" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J178" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K178" s="5">
+        <v>2340</v>
+      </c>
+      <c r="L178" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M178" s="5">
+        <v>1166</v>
+      </c>
+      <c r="N178" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="O178" s="5">
+        <v>775</v>
+      </c>
+      <c r="P178" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="Q178" s="5">
+        <v>532</v>
+      </c>
+      <c r="R178" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="S178" s="5">
+        <v>262</v>
+      </c>
+      <c r="T178" s="4" t="s">
+        <v>1571</v>
+      </c>
+      <c r="U178" s="5">
+        <v>144</v>
+      </c>
+      <c r="V178" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="W178" s="5">
+        <v>28</v>
+      </c>
+      <c r="X178" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="Y178" s="5">
+        <v>262</v>
+      </c>
+      <c r="Z178" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA178" s="5">
+        <v>144</v>
+      </c>
+      <c r="AB178" s="4" t="s">
+        <v>1574</v>
+      </c>
+      <c r="AC178" s="5">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="179" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="193" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="194" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="195" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -21550,7 +21750,12 @@
     <row r="230" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E178" r:id="rId1"/>
+    <hyperlink ref="D178" r:id="rId2"/>
+    <hyperlink ref="G178" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="1594">
   <si>
     <t>Facebook</t>
   </si>
@@ -6059,6 +6059,110 @@
   </si>
   <si>
     <t>終生卡</t>
+  </si>
+  <si>
+    <t>神代紀事</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ShindaiRecord</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.IceDragon.ShindaiRecord&amp;hl=zh_TW&amp;fbclid=IwY2xjawL8VbpleHRuA2FlbQIxMABicmlkETFMUEUzeWpMQUVnbUQxTW9FAR5khHVT2YUhE5xhO2B-MJL1ODx1zBZJcQeA0AGIDh_XBZzK6PEnlyENRfzI7A_aem_gXLvCoTZUoscSpWEZ4hYxg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/us/app/%E7%A5%9E%E4%BB%A3%E7%B4%80%E4%BA%8B-%E5%83%8F%E7%B4%A0%E9%A2%A8roguelike%E9%81%8A%E6%88%B2/id6720742591</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《神代紀事》是一款像素風</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Roguelite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冒險</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，採單手直立式操控，讓您隨時沉浸在神話世界。探索隨機地圖，組合百種技能與多樣武器，挑戰生存極限。官方時常發布禮包碼，讓玩家能免費兌換豐富資源，享受開局優勢。遊戲主要考驗技術與策略，但透過適度的儲值則可加速角色成長或解鎖限定道具，讓您的冒險旅程更加個人化。立即化身啟源者，善用免費禮包碼福利與儲值助力，與朋友連線，共同寫下不朽的戰鬥史詩！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/Co.php?bsn=60076&amp;sn=103640542</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500+150起源石</t>
+  </si>
+  <si>
+    <t>250+50起源石</t>
+  </si>
+  <si>
+    <t>150+15起源石</t>
+  </si>
+  <si>
+    <t>75+5起源石</t>
+  </si>
+  <si>
+    <t>25起源石</t>
+  </si>
+  <si>
+    <t>5起源石</t>
+  </si>
+  <si>
+    <t>冒險補給</t>
+  </si>
+  <si>
+    <t>每月限購禮包</t>
+  </si>
+  <si>
+    <t>每周限購禮包</t>
+  </si>
+  <si>
+    <t>每日限購禮包</t>
+  </si>
+  <si>
+    <t>超值自選包</t>
+  </si>
+  <si>
+    <t>超值腳色包</t>
+  </si>
+  <si>
+    <t>新手啟程包</t>
   </si>
 </sst>
 </file>
@@ -17539,7 +17643,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H178" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H179" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20487,7 +20591,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F178" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F179" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -21556,7 +21660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="29" t="s">
         <v>1544</v>
       </c>
@@ -21608,7 +21712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="35" t="s">
         <v>1560</v>
       </c>
@@ -21696,20 +21800,125 @@
         <v>775</v>
       </c>
     </row>
-    <row r="179" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="35" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C179" s="37" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D179" s="36" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E179" s="36" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F179" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=神代紀事</v>
+      </c>
+      <c r="G179" s="36" t="s">
+        <v>1580</v>
+      </c>
+      <c r="H179" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=神代紀事</v>
+      </c>
+      <c r="I179" s="24" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J179" s="4" t="s">
+        <v>1581</v>
+      </c>
+      <c r="K179" s="5">
+        <v>2340</v>
+      </c>
+      <c r="L179" s="4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="M179" s="5">
+        <v>1166</v>
+      </c>
+      <c r="N179" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="O179" s="5">
+        <v>697</v>
+      </c>
+      <c r="P179" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="Q179" s="5">
+        <v>357</v>
+      </c>
+      <c r="R179" s="4" t="s">
+        <v>1585</v>
+      </c>
+      <c r="S179" s="5">
+        <v>127</v>
+      </c>
+      <c r="T179" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="U179" s="5">
+        <v>25</v>
+      </c>
+      <c r="V179" s="4" t="s">
+        <v>1587</v>
+      </c>
+      <c r="W179" s="5">
+        <v>230</v>
+      </c>
+      <c r="X179" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="Y179" s="5">
+        <v>697</v>
+      </c>
+      <c r="Z179" s="4" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AA179" s="5">
+        <v>230</v>
+      </c>
+      <c r="AB179" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="AC179" s="5">
+        <v>25</v>
+      </c>
+      <c r="AD179" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="AE179" s="5">
+        <v>357</v>
+      </c>
+      <c r="AF179" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="AG179" s="5">
+        <v>127</v>
+      </c>
+      <c r="AH179" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="AI179" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="193" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="194" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="195" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -21754,8 +21963,12 @@
     <hyperlink ref="E178" r:id="rId1"/>
     <hyperlink ref="D178" r:id="rId2"/>
     <hyperlink ref="G178" r:id="rId3"/>
+    <hyperlink ref="C179" r:id="rId4"/>
+    <hyperlink ref="D179" r:id="rId5"/>
+    <hyperlink ref="E179" r:id="rId6"/>
+    <hyperlink ref="G179" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="1594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="1606">
   <si>
     <t>Facebook</t>
   </si>
@@ -6163,6 +6163,47 @@
   </si>
   <si>
     <t>新手啟程包</t>
+  </si>
+  <si>
+    <t>天命國度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《天命國度 》是 IGG 匠心打造的史詩級策略手遊。在這個奇幻大陸上，您將化身領主，從零開始建造宏偉王國，集結傳說英雄，與全球菁英玩家展開即時策略對決。遊戲不僅考驗您的戰術佈局，更重視資源的累積與運用。想在開戰時取得優勢，記得隨時關注官方釋出的最新禮包碼，並可尋找可靠的代儲值管道來極大化您的資源效益，讓您的王國以前所未有的速度崛起，稱霸全服！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fatewar.igg.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/fate-war/id1632729482</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/FateWar/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/B.php?bsn=82987</t>
+  </si>
+  <si>
+    <t>9999黃金</t>
+  </si>
+  <si>
+    <t>4999黃金</t>
+  </si>
+  <si>
+    <t>999黃金</t>
+  </si>
+  <si>
+    <t>499黃金</t>
+  </si>
+  <si>
+    <t>99黃金</t>
+  </si>
+  <si>
+    <t>內政廳基金</t>
   </si>
 </sst>
 </file>
@@ -17643,7 +17684,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H179" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H180" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20591,7 +20632,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F179" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F180" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -21906,7 +21947,70 @@
         <v>25</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="35" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C180" s="37" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D180" s="36" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E180" s="36" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F180" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=天命國度</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H180" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=天命國度</v>
+      </c>
+      <c r="I180" s="31" t="s">
+        <v>1595</v>
+      </c>
+      <c r="J180" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="K180" s="5">
+        <v>2539</v>
+      </c>
+      <c r="L180" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="M180" s="5">
+        <v>1323</v>
+      </c>
+      <c r="N180" s="4" t="s">
+        <v>1602</v>
+      </c>
+      <c r="O180" s="5">
+        <v>262</v>
+      </c>
+      <c r="P180" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="Q180" s="5">
+        <v>144</v>
+      </c>
+      <c r="R180" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="S180" s="5">
+        <v>28</v>
+      </c>
+      <c r="T180" s="4" t="s">
+        <v>1605</v>
+      </c>
+      <c r="U180" s="5">
+        <v>532</v>
+      </c>
+    </row>
     <row r="181" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="182" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="183" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -21967,8 +22071,11 @@
     <hyperlink ref="D179" r:id="rId5"/>
     <hyperlink ref="E179" r:id="rId6"/>
     <hyperlink ref="G179" r:id="rId7"/>
+    <hyperlink ref="D180" r:id="rId8"/>
+    <hyperlink ref="E180" r:id="rId9"/>
+    <hyperlink ref="C180" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="1606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="1637">
   <si>
     <t>Facebook</t>
   </si>
@@ -6204,6 +6204,151 @@
   </si>
   <si>
     <t>內政廳基金</t>
+  </si>
+  <si>
+    <t>戰國武士道</t>
+  </si>
+  <si>
+    <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，織田信長、豐臣秀吉、德川家康等傳奇武將悉數登場，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sengokubushido.daimaoo.com/?fbclid=IwY2xjawMAQbRleHRuA2FlbQIxMABicmlkETFPYlJ3QnBHdzJ2ZHpqTTR1AR6zM1yhT-zsCARVzhipU4ZQmqlUO1mnmbLB2-ADjU0f2LHx6kokbFYlE-eang_aem_yul5hCIFGTcCd7GAYVQ0Ug</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/senbushi</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%88%B0%E5%9C%8B%E6%AD%A6%E5%A3%AB%E9%81%93-%E5%A4%A7%E9%87%8E%E6%9C%9B%E4%B9%8B%E5%8D%B7/id6744687916</t>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/B.php?bsn=83113</t>
+  </si>
+  <si>
+    <r>
+      <t>《超蝦大作戰》是一款充滿趣味與創意的休閒放置養成遊戲。玩家將進入一個奇妙的異世界，從一顆蝦蛋開始，透過不斷吞噬與進化，培養出千奇百怪、戰力爆表的究極神蝦。遊戲畫風搞怪可愛，玩法輕鬆上手，您將見證小蝦米如何一步步變異，解鎖各種腦洞大開的基因形態，最終成為稱霸水域的蝦界王者。為了幫助您的神蝦快速成長，記得要隨時關注並領取官方發布的最新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換免費的鑽石和加速道具。遊戲內也提供便捷的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。快來加入這場超展開的蝦世界冒險，看看你的蝦能進化到多狂！</t>
+    </r>
+  </si>
+  <si>
+    <t>超蝦大作戰</t>
+  </si>
+  <si>
+    <t>https://acg.gamer.com.tw/acgDetail.php?s=146280</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/overbrawl.go</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://overbrawl.knetgame.com/pre</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%B6%85%E8%9D%A6%E5%A4%A7%E4%BD%9C%E6%88%B0/id6746176096</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4600判金</t>
+  </si>
+  <si>
+    <t>9000判金</t>
+  </si>
+  <si>
+    <t>2650判金</t>
+  </si>
+  <si>
+    <t>1300判金</t>
+  </si>
+  <si>
+    <t>420判金</t>
+  </si>
+  <si>
+    <t>70判金</t>
+  </si>
+  <si>
+    <t>日本朱印狀</t>
+  </si>
+  <si>
+    <t>戰國朱印狀</t>
+  </si>
+  <si>
+    <t>守護朱印狀</t>
+  </si>
+  <si>
+    <t>US$99.99商品</t>
+  </si>
+  <si>
+    <t>US$69.99商品</t>
+  </si>
+  <si>
+    <t>US$49.99商品</t>
+  </si>
+  <si>
+    <t>US$29.99商品</t>
+  </si>
+  <si>
+    <t>US$19.99商品</t>
+  </si>
+  <si>
+    <t>US$14.99商品</t>
+  </si>
+  <si>
+    <t>US$9.99商品</t>
+  </si>
+  <si>
+    <t>US$8.99商品</t>
+  </si>
+  <si>
+    <t>US$4.99商品</t>
+  </si>
+  <si>
+    <t>US$3.99商品</t>
   </si>
 </sst>
 </file>
@@ -17684,7 +17829,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H180" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H182" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20632,7 +20777,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F180" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F182" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -22011,8 +22156,176 @@
         <v>532</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="30" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D181" s="36" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F181" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=戰國武士道</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H181" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=戰國武士道</v>
+      </c>
+      <c r="I181" s="34" t="s">
+        <v>1607</v>
+      </c>
+      <c r="J181" s="4" t="s">
+        <v>1619</v>
+      </c>
+      <c r="K181" s="5">
+        <v>2539</v>
+      </c>
+      <c r="L181" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="M181" s="5">
+        <v>1323</v>
+      </c>
+      <c r="N181" s="4" t="s">
+        <v>1620</v>
+      </c>
+      <c r="O181" s="5">
+        <v>783</v>
+      </c>
+      <c r="P181" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="Q181" s="5">
+        <v>397</v>
+      </c>
+      <c r="R181" s="4" t="s">
+        <v>1622</v>
+      </c>
+      <c r="S181" s="5">
+        <v>144</v>
+      </c>
+      <c r="T181" s="4" t="s">
+        <v>1623</v>
+      </c>
+      <c r="U181" s="5">
+        <v>25</v>
+      </c>
+      <c r="V181" s="4" t="s">
+        <v>1624</v>
+      </c>
+      <c r="W181" s="5">
+        <v>1252</v>
+      </c>
+      <c r="X181" s="4" t="s">
+        <v>1625</v>
+      </c>
+      <c r="Y181" s="5">
+        <v>135</v>
+      </c>
+      <c r="Z181" s="4" t="s">
+        <v>1626</v>
+      </c>
+      <c r="AA181" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="182" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="30" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C182" s="37" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D182" s="36" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E182" s="36" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F182" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=超蝦大作戰</v>
+      </c>
+      <c r="G182" s="36" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H182" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=超蝦大作戰</v>
+      </c>
+      <c r="I182" t="s">
+        <v>1612</v>
+      </c>
+      <c r="J182" s="4" t="s">
+        <v>1627</v>
+      </c>
+      <c r="K182" s="5">
+        <v>2539</v>
+      </c>
+      <c r="L182" s="4" t="s">
+        <v>1628</v>
+      </c>
+      <c r="M182" s="5">
+        <v>1793</v>
+      </c>
+      <c r="N182" s="4" t="s">
+        <v>1629</v>
+      </c>
+      <c r="O182" s="5">
+        <v>1323</v>
+      </c>
+      <c r="P182" s="4" t="s">
+        <v>1630</v>
+      </c>
+      <c r="Q182" s="5">
+        <v>775</v>
+      </c>
+      <c r="R182" s="4" t="s">
+        <v>1631</v>
+      </c>
+      <c r="S182" s="5">
+        <v>532</v>
+      </c>
+      <c r="T182" s="4" t="s">
+        <v>1632</v>
+      </c>
+      <c r="U182" s="5">
+        <v>389</v>
+      </c>
+      <c r="V182" s="4" t="s">
+        <v>1633</v>
+      </c>
+      <c r="W182" s="5">
+        <v>262</v>
+      </c>
+      <c r="X182" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="Y182" s="5">
+        <v>238</v>
+      </c>
+      <c r="Z182" s="4" t="s">
+        <v>1635</v>
+      </c>
+      <c r="AA182" s="5">
+        <v>144</v>
+      </c>
+      <c r="AB182" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="AC182" s="5">
+        <v>110</v>
+      </c>
+    </row>
     <row r="183" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="184" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="185" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22074,8 +22387,13 @@
     <hyperlink ref="D180" r:id="rId8"/>
     <hyperlink ref="E180" r:id="rId9"/>
     <hyperlink ref="C180" r:id="rId10"/>
+    <hyperlink ref="D181" r:id="rId11"/>
+    <hyperlink ref="G182" r:id="rId12"/>
+    <hyperlink ref="C182" r:id="rId13"/>
+    <hyperlink ref="D182" r:id="rId14"/>
+    <hyperlink ref="E182" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -6209,10 +6209,6 @@
     <t>戰國武士道</t>
   </si>
   <si>
-    <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，織田信長、豐臣秀吉、德川家康等傳奇武將悉數登場，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://sengokubushido.daimaoo.com/?fbclid=IwY2xjawMAQbRleHRuA2FlbQIxMABicmlkETFPYlJ3QnBHdzJ2ZHpqTTR1AR6zM1yhT-zsCARVzhipU4ZQmqlUO1mnmbLB2-ADjU0f2LHx6kokbFYlE-eang_aem_yul5hCIFGTcCd7GAYVQ0Ug</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6224,6 +6220,82 @@
   </si>
   <si>
     <t>https://forum.gamer.com.tw/B.php?bsn=83113</t>
+  </si>
+  <si>
+    <t>超蝦大作戰</t>
+  </si>
+  <si>
+    <t>https://acg.gamer.com.tw/acgDetail.php?s=146280</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/overbrawl.go</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://overbrawl.knetgame.com/pre</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%B6%85%E8%9D%A6%E5%A4%A7%E4%BD%9C%E6%88%B0/id6746176096</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4600判金</t>
+  </si>
+  <si>
+    <t>9000判金</t>
+  </si>
+  <si>
+    <t>2650判金</t>
+  </si>
+  <si>
+    <t>1300判金</t>
+  </si>
+  <si>
+    <t>420判金</t>
+  </si>
+  <si>
+    <t>70判金</t>
+  </si>
+  <si>
+    <t>日本朱印狀</t>
+  </si>
+  <si>
+    <t>戰國朱印狀</t>
+  </si>
+  <si>
+    <t>守護朱印狀</t>
+  </si>
+  <si>
+    <t>US$99.99商品</t>
+  </si>
+  <si>
+    <t>US$69.99商品</t>
+  </si>
+  <si>
+    <t>US$49.99商品</t>
+  </si>
+  <si>
+    <t>US$29.99商品</t>
+  </si>
+  <si>
+    <t>US$19.99商品</t>
+  </si>
+  <si>
+    <t>US$14.99商品</t>
+  </si>
+  <si>
+    <t>US$9.99商品</t>
+  </si>
+  <si>
+    <t>US$8.99商品</t>
+  </si>
+  <si>
+    <t>US$4.99商品</t>
+  </si>
+  <si>
+    <t>US$3.99商品</t>
   </si>
   <si>
     <r>
@@ -6271,84 +6343,13 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。快來加入這場超展開的蝦世界冒險，看看你的蝦能進化到多狂！</t>
+      <t>服務，讓您能獲得稀有資源，輕鬆碾壓對手，享受最蝦趴的進化之旅。</t>
     </r>
-  </si>
-  <si>
-    <t>超蝦大作戰</t>
-  </si>
-  <si>
-    <t>https://acg.gamer.com.tw/acgDetail.php?s=146280</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/overbrawl.go</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://overbrawl.knetgame.com/pre</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E8%B6%85%E8%9D%A6%E5%A4%A7%E4%BD%9C%E6%88%B0/id6746176096</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4600判金</t>
-  </si>
-  <si>
-    <t>9000判金</t>
-  </si>
-  <si>
-    <t>2650判金</t>
-  </si>
-  <si>
-    <t>1300判金</t>
-  </si>
-  <si>
-    <t>420判金</t>
-  </si>
-  <si>
-    <t>70判金</t>
-  </si>
-  <si>
-    <t>日本朱印狀</t>
-  </si>
-  <si>
-    <t>戰國朱印狀</t>
-  </si>
-  <si>
-    <t>守護朱印狀</t>
-  </si>
-  <si>
-    <t>US$99.99商品</t>
-  </si>
-  <si>
-    <t>US$69.99商品</t>
-  </si>
-  <si>
-    <t>US$49.99商品</t>
-  </si>
-  <si>
-    <t>US$29.99商品</t>
-  </si>
-  <si>
-    <t>US$19.99商品</t>
-  </si>
-  <si>
-    <t>US$14.99商品</t>
-  </si>
-  <si>
-    <t>US$9.99商品</t>
-  </si>
-  <si>
-    <t>US$8.99商品</t>
-  </si>
-  <si>
-    <t>US$4.99商品</t>
-  </si>
-  <si>
-    <t>US$3.99商品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22161,78 +22162,78 @@
         <v>1606</v>
       </c>
       <c r="C181" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D181" s="36" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E181" s="2" t="s">
         <v>1609</v>
-      </c>
-      <c r="D181" s="36" t="s">
-        <v>1608</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>1610</v>
       </c>
       <c r="F181" s="11" t="str">
         <f t="shared" si="6"/>
         <v>gift-codes.html?game=戰國武士道</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H181" s="13" t="str">
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=戰國武士道</v>
       </c>
       <c r="I181" s="34" t="s">
-        <v>1607</v>
+        <v>1636</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="K181" s="5">
         <v>2539</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M181" s="5">
         <v>1323</v>
       </c>
       <c r="N181" s="4" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="O181" s="5">
         <v>783</v>
       </c>
       <c r="P181" s="4" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="Q181" s="5">
         <v>397</v>
       </c>
       <c r="R181" s="4" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="S181" s="5">
         <v>144</v>
       </c>
       <c r="T181" s="4" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="U181" s="5">
         <v>25</v>
       </c>
       <c r="V181" s="4" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="W181" s="5">
         <v>1252</v>
       </c>
       <c r="X181" s="4" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="Y181" s="5">
         <v>135</v>
       </c>
       <c r="Z181" s="4" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="AA181" s="5">
         <v>85</v>
@@ -22240,87 +22241,87 @@
     </row>
     <row r="182" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="30" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C182" s="37" t="s">
         <v>1613</v>
       </c>
-      <c r="C182" s="37" t="s">
+      <c r="D182" s="36" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E182" s="36" t="s">
         <v>1615</v>
-      </c>
-      <c r="D182" s="36" t="s">
-        <v>1616</v>
-      </c>
-      <c r="E182" s="36" t="s">
-        <v>1617</v>
       </c>
       <c r="F182" s="11" t="str">
         <f t="shared" si="6"/>
         <v>gift-codes.html?game=超蝦大作戰</v>
       </c>
       <c r="G182" s="36" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="H182" s="13" t="str">
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=超蝦大作戰</v>
       </c>
       <c r="I182" t="s">
-        <v>1612</v>
+        <v>1635</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="K182" s="5">
         <v>2539</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="M182" s="5">
         <v>1793</v>
       </c>
       <c r="N182" s="4" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="O182" s="5">
         <v>1323</v>
       </c>
       <c r="P182" s="4" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="Q182" s="5">
         <v>775</v>
       </c>
       <c r="R182" s="4" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="S182" s="5">
         <v>532</v>
       </c>
       <c r="T182" s="4" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="U182" s="5">
         <v>389</v>
       </c>
       <c r="V182" s="4" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="W182" s="5">
         <v>262</v>
       </c>
       <c r="X182" s="4" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="Y182" s="5">
         <v>238</v>
       </c>
       <c r="Z182" s="4" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="AA182" s="5">
         <v>144</v>
       </c>
       <c r="AB182" s="4" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AC182" s="5">
         <v>110</v>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="1649">
   <si>
     <t>Facebook</t>
   </si>
@@ -6350,6 +6350,87 @@
   <si>
     <t>《戰國武士道》是一款引人入勝的日本戰國策略手機遊戲，讓玩家化身為一方大名，體驗從崛起到統一天下的完整歷程。遊戲深度還原了戰國時代的歷史風貌，等待您的招募與調遣。玩家需要精通內政管理、發展城池，同時運籌帷幄，指揮麾下部隊進行合戰。想在亂世中快速脫穎而出，記得要多加利用最新的禮包碼兌換豐富資源，讓您的開局更加順利。遊戲也提供了便利的儲值系統，讓您可以更快速地強化部隊與城防，加速實現統一日本的「大野望」。立即投身這個風起雲湧的時代，開創屬於您的霸業傳奇！</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真妖獸!廢柴要修仙</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/TW.realmonster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E7%9C%9F%E5%A6%96%E7%8D%B8-%E5%BB%A2%E6%9F%B4%E8%A6%81%E4%BF%AE%E4%BB%99/id6747165987</t>
+  </si>
+  <si>
+    <t>https://www.itrimen.com/</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>準備好踏上顛覆傳統的修仙之旅嗎？《真妖獸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>廢柴要修仙》是一款讓你從廢柴逆襲成仙的放置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>RPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。遊戲以「渡劫飛升」與「降妖伏魔」為核心玩法，帶來最刺激的修仙體驗。你將在仙俠世界收服奇珍異獸，不斷修煉突破。為了助你快速提升實力，官方時常提供豐富的禮包碼，輕鬆獲取大量資源。遊戲的煉丹、煉器與洞府等養成系統極具深度。若想在仙途上領先，安全的代儲值服務能讓你迅速累積優勢，解鎖強力法寶與稀有妖獸，打造你的修仙傳奇，成為三界主宰！立即下載，開啟你的逆天修行路。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6660仙玉</t>
+  </si>
+  <si>
+    <t>2000仙玉</t>
+  </si>
+  <si>
+    <t>1300仙玉</t>
+  </si>
+  <si>
+    <t>680仙玉</t>
+  </si>
+  <si>
+    <t>330仙玉</t>
+  </si>
+  <si>
+    <t>130仙玉</t>
   </si>
 </sst>
 </file>
@@ -17830,7 +17911,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H182" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H183" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20778,7 +20859,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F182" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F183" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -22327,7 +22408,82 @@
         <v>110</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="30" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C183" s="37" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E183" s="36" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F183" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=真妖獸!廢柴要修仙</v>
+      </c>
+      <c r="G183" s="36" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H183" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=真妖獸!廢柴要修仙</v>
+      </c>
+      <c r="I183" s="24" t="s">
+        <v>1641</v>
+      </c>
+      <c r="J183" s="4" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K183" s="5">
+        <v>2539</v>
+      </c>
+      <c r="L183" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="M183" s="5">
+        <v>1323</v>
+      </c>
+      <c r="N183" s="4" t="s">
+        <v>1644</v>
+      </c>
+      <c r="O183" s="5">
+        <v>775</v>
+      </c>
+      <c r="P183" s="4" t="s">
+        <v>1645</v>
+      </c>
+      <c r="Q183" s="5">
+        <v>532</v>
+      </c>
+      <c r="R183" s="4" t="s">
+        <v>1646</v>
+      </c>
+      <c r="S183" s="5">
+        <v>262</v>
+      </c>
+      <c r="T183" s="4" t="s">
+        <v>1647</v>
+      </c>
+      <c r="U183" s="5">
+        <v>144</v>
+      </c>
+      <c r="V183" s="4" t="s">
+        <v>1648</v>
+      </c>
+      <c r="W183" s="5">
+        <v>59</v>
+      </c>
+      <c r="X183" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="Y183" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="184" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="185" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="186" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22393,8 +22549,10 @@
     <hyperlink ref="C182" r:id="rId13"/>
     <hyperlink ref="D182" r:id="rId14"/>
     <hyperlink ref="E182" r:id="rId15"/>
+    <hyperlink ref="C183" r:id="rId16"/>
+    <hyperlink ref="G183" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="1649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="1656">
   <si>
     <t>Facebook</t>
   </si>
@@ -6431,6 +6431,78 @@
   </si>
   <si>
     <t>130仙玉</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E4%B8%89%E5%9C%8B%E5%BF%97thrones/id6741511767</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.statewill.shzz</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61575005136218</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/#</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>《三國志Thrones》是一款讓您身歷其境的策略手遊，完美還原三國時代的壯闊史詩。遊戲中，您將扮演一方之主，從零開始建立您的城池，招募關羽、張飛、趙雲等傳奇武將，並透過合縱連橫的外交手段，與其他玩家結盟或對抗，最終目標是稱霸天下。遊戲畫面精緻，戰鬥場景氣勢磅礡，讓您體驗最真實的三國戰爭。想要快速提升實力，除了透過</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>獲得更多資源，也別忘了尋找最新的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換豐富的虛寶獎勵，讓您的統一天下之路更加順遂！立即下載《三國志Thrones》，開啟您的三國霸業！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三國志Thrones</t>
+  </si>
+  <si>
+    <t>980元寶</t>
   </si>
 </sst>
 </file>
@@ -17911,7 +17983,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H183" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H184" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20859,7 +20931,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F183" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F184" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -22484,7 +22556,70 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C184" s="37" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D184" s="36" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E184" s="36" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F184" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=三國志Thrones</v>
+      </c>
+      <c r="G184" s="36" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H184" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=三國志Thrones</v>
+      </c>
+      <c r="I184" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J184" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K184" s="5">
+        <v>3010</v>
+      </c>
+      <c r="L184" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="M184" s="5">
+        <v>1550</v>
+      </c>
+      <c r="N184" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="O184" s="5">
+        <v>932</v>
+      </c>
+      <c r="P184" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="Q184" s="5">
+        <v>475</v>
+      </c>
+      <c r="R184" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="S184" s="5">
+        <v>156</v>
+      </c>
+      <c r="T184" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="U184" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="185" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="186" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="187" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22551,8 +22686,12 @@
     <hyperlink ref="E182" r:id="rId15"/>
     <hyperlink ref="C183" r:id="rId16"/>
     <hyperlink ref="G183" r:id="rId17"/>
+    <hyperlink ref="E184" r:id="rId18"/>
+    <hyperlink ref="D184" r:id="rId19"/>
+    <hyperlink ref="C184" r:id="rId20"/>
+    <hyperlink ref="G184" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1663">
   <si>
     <t>Facebook</t>
   </si>
@@ -6503,6 +6503,32 @@
   </si>
   <si>
     <t>980元寶</t>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/B.php?bsn=79185</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄之地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.orienjoy.heroland&amp;hl=ln</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61577308460249</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/cn/app/%E8%8B%B1%E5%8B%87%E4%B9%8B%E5%9C%B0/id6480160896</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>晨輝新星時裝</t>
+  </si>
+  <si>
+    <t>晨輝靈獅時裝</t>
   </si>
 </sst>
 </file>
@@ -17983,7 +18009,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H184" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H185" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20931,7 +20957,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F184" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F185" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -22620,7 +22646,91 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="31" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C185" s="37" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D185" s="36" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E185" s="36" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F185" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=英雄之地</v>
+      </c>
+      <c r="G185" s="36" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H185" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=英雄之地</v>
+      </c>
+      <c r="J185" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K185" s="5">
+        <v>2539</v>
+      </c>
+      <c r="L185" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M185" s="5">
+        <v>1323</v>
+      </c>
+      <c r="N185" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O185" s="5">
+        <v>775</v>
+      </c>
+      <c r="P185" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q185" s="5">
+        <v>389</v>
+      </c>
+      <c r="R185" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S185" s="5">
+        <v>144</v>
+      </c>
+      <c r="T185" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="U185" s="5">
+        <v>25</v>
+      </c>
+      <c r="V185" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="W185" s="5">
+        <v>144</v>
+      </c>
+      <c r="X185" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="Y185" s="5">
+        <v>389</v>
+      </c>
+      <c r="Z185" s="4" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AA185" s="5">
+        <v>1166</v>
+      </c>
+      <c r="AB185" s="4" t="s">
+        <v>1662</v>
+      </c>
+      <c r="AC185" s="5">
+        <v>476</v>
+      </c>
+    </row>
     <row r="186" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="187" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="188" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22690,8 +22800,12 @@
     <hyperlink ref="D184" r:id="rId19"/>
     <hyperlink ref="C184" r:id="rId20"/>
     <hyperlink ref="G184" r:id="rId21"/>
+    <hyperlink ref="G185" r:id="rId22"/>
+    <hyperlink ref="D185" r:id="rId23"/>
+    <hyperlink ref="C185" r:id="rId24"/>
+    <hyperlink ref="E185" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1664">
   <si>
     <t>Facebook</t>
   </si>
@@ -6529,6 +6529,36 @@
   </si>
   <si>
     <t>晨輝靈獅時裝</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《英勇之地》是一款奇幻風格的輕度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Roguelike RPG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">動作冒險手遊。玩家將扮演一位英勇的騎士，在充滿挑戰的奇幻世界中，探索地圖、收集裝備與技能，並與各種怪物戰鬥。遊戲主打流暢的戰鬥體驗與多樣化的職業和技能組合，讓每場冒險都充滿未知與驚喜。透過不斷挑戰關卡，提升角色等級，並利用強大的裝備與技能來擊敗最終頭目。遊戲內提供多種禮包碼供玩家兌換豐富獎勵，同時也支援多樣化的代儲值管道，讓玩家能輕鬆獲得更多資源，快速增強戰力，享受更加暢快的遊戲樂趣。
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22670,6 +22700,9 @@
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=英雄之地</v>
       </c>
+      <c r="I185" s="24" t="s">
+        <v>1663</v>
+      </c>
       <c r="J185" s="4" t="s">
         <v>13</v>
       </c>

--- a/games.xlsx
+++ b/games.xlsx
@@ -6509,10 +6509,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>英雄之地</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://play.google.com/store/apps/details?id=com.orienjoy.heroland&amp;hl=ln</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6559,6 +6555,9 @@
 </t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英勇之地</t>
   </si>
 </sst>
 </file>
@@ -22676,32 +22675,32 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="31" t="s">
+    <row r="185" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="30" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C185" s="37" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D185" s="36" t="s">
         <v>1657</v>
       </c>
-      <c r="C185" s="37" t="s">
+      <c r="E185" s="36" t="s">
         <v>1659</v>
-      </c>
-      <c r="D185" s="36" t="s">
-        <v>1658</v>
-      </c>
-      <c r="E185" s="36" t="s">
-        <v>1660</v>
       </c>
       <c r="F185" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>gift-codes.html?game=英雄之地</v>
+        <v>gift-codes.html?game=英勇之地</v>
       </c>
       <c r="G185" s="36" t="s">
         <v>1656</v>
       </c>
       <c r="H185" s="13" t="str">
         <f t="shared" si="5"/>
-        <v>https://www.ssbuy.tw/game-detail.html?game=英雄之地</v>
+        <v>https://www.ssbuy.tw/game-detail.html?game=英勇之地</v>
       </c>
       <c r="I185" s="24" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>13</v>
@@ -22752,13 +22751,13 @@
         <v>389</v>
       </c>
       <c r="Z185" s="4" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="AA185" s="5">
         <v>1166</v>
       </c>
       <c r="AB185" s="4" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="AC185" s="5">
         <v>476</v>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="1689">
   <si>
     <t>Facebook</t>
   </si>
@@ -6558,6 +6558,113 @@
   </si>
   <si>
     <t>英勇之地</t>
+  </si>
+  <si>
+    <t>未鑑定勇者團</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰靈異聞社</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《未鑑定勇者團》是一款像素風格的放置型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RPG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手遊，帶您進入一個充滿懷舊與冒險的奇幻世界。遊戲核心特色在於其獨特的「未鑑定」系統，玩家將招募各種職業的勇者，他們的能力與潛力都是未知的，需要透過您的細心培養和鑑定，才能發掘出最強大的隱藏英雄。遊戲玩法輕鬆，即使離線也能持續獲得收益，讓您輕鬆養成您的勇者隊伍。為了讓您的冒險之路更加順暢，別忘了隨時查找最新的禮包碼，兌換豐富的虛寶獎勵，快速提升戰力。若想在遊戲中取得更多優勢，也可以考慮使用安全的代儲值服務，輕鬆獲取鑽石與各種稀有道具，打造無堅不摧的傳奇勇者團。立即加入，揭開所有未鑑定勇者的神秘面紗，展開一場獨一無二的冒險旅程！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《戰靈異聞社》是一款都市怪談風格的卡牌放置手遊。遊戲將您帶入一個現代與靈異交織的世界，您將扮演「異聞社」的社長，專門解決各種超自然事件。遊戲美術風格獨特，融合了潮流與傳統元素，打造出百位以上各具特色的「戰靈」。玩家需要策略性地組合隊伍，利用戰靈之間的羈絆與技能，挑戰各種詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌之餘也能享受卡牌養成的樂趣。官方經常發放福利，記得要關注社群平台領取最新的禮包碼，強化您的戰靈隊伍。對於追求極致遊戲體驗的玩家，尋找可靠的代儲值管道能幫助您更快地收集心儀角色，解鎖更強大的力量，帶領您的異聞社，揭開所有神秘事件背後的真相。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.dreamplay.hiddenheroes.google&amp;fbclid=IwY2xjawMIIqZleHRuA2FlbQIxMABicmlkETFkZXV4UHJOSGFrcm92WWVYAR4-fZWlGr15cqSHFRjjaQwTW4OE4HDAfdBZ5LKH4DG9IgD3Tidgy-Udr-Yk3w_aem_evKrdZdXYqQCCS1J3i2qBg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/%E6%9C%AA%E9%91%91%E5%AE%9A%E5%8B%87%E8%80%85%E5%9C%98-%E9%81%8B%E6%B0%A3%E5%9E%8B%E6%94%BE%E7%BD%AErpg/id6744206189</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61577386190686</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/B.php?bsn=83087</t>
+  </si>
+  <si>
+    <t>https://soul.staroio.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/SpiritTaleSociety</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%88%B0%E9%9D%88%E7%95%B0%E8%81%9E%E7%A4%BE/id6745178365</t>
+  </si>
+  <si>
+    <t>13000翡翠</t>
+  </si>
+  <si>
+    <t>3450翡翠</t>
+  </si>
+  <si>
+    <t>600翡翠</t>
+  </si>
+  <si>
+    <t>難度通行證</t>
+  </si>
+  <si>
+    <t>勇者等級通行證</t>
+  </si>
+  <si>
+    <t>99.99禮包</t>
+  </si>
+  <si>
+    <t>49.99禮包</t>
+  </si>
+  <si>
+    <t>29.99禮包</t>
+  </si>
+  <si>
+    <t>19.99禮包</t>
+  </si>
+  <si>
+    <t>14.99禮包</t>
+  </si>
+  <si>
+    <t>12.99禮包</t>
+  </si>
+  <si>
+    <t>9.99禮包</t>
+  </si>
+  <si>
+    <t>4.99禮包</t>
+  </si>
+  <si>
+    <t>0.99禮包</t>
   </si>
 </sst>
 </file>
@@ -18038,7 +18145,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H185" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H187" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -20986,7 +21093,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F185" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F187" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -22763,8 +22870,146 @@
         <v>476</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="32" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C186" s="37" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D186" s="36" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E186" s="36" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F186" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=未鑑定勇者團</v>
+      </c>
+      <c r="G186" s="36" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H186" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=未鑑定勇者團</v>
+      </c>
+      <c r="I186" s="24" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J186" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K186" s="5">
+        <v>2355</v>
+      </c>
+      <c r="L186" s="4" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M186" s="5">
+        <v>937</v>
+      </c>
+      <c r="N186" s="4" t="s">
+        <v>1677</v>
+      </c>
+      <c r="O186" s="5">
+        <v>232</v>
+      </c>
+      <c r="P186" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="Q186" s="5">
+        <v>176</v>
+      </c>
+      <c r="R186" s="4" t="s">
+        <v>1679</v>
+      </c>
+      <c r="S186" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="187" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="32" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F187" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=戰靈異聞社</v>
+      </c>
+      <c r="G187" s="36" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H187" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=戰靈異聞社</v>
+      </c>
+      <c r="I187" s="34" t="s">
+        <v>1667</v>
+      </c>
+      <c r="J187" s="4" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K187" s="5">
+        <v>2555</v>
+      </c>
+      <c r="L187" s="4" t="s">
+        <v>1681</v>
+      </c>
+      <c r="M187" s="5">
+        <v>1331</v>
+      </c>
+      <c r="N187" s="4" t="s">
+        <v>1682</v>
+      </c>
+      <c r="O187" s="5">
+        <v>788</v>
+      </c>
+      <c r="P187" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="Q187" s="5">
+        <v>535</v>
+      </c>
+      <c r="R187" s="4" t="s">
+        <v>1684</v>
+      </c>
+      <c r="S187" s="5">
+        <v>391</v>
+      </c>
+      <c r="T187" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="U187" s="5">
+        <v>343</v>
+      </c>
+      <c r="V187" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="W187" s="5">
+        <v>264</v>
+      </c>
+      <c r="X187" s="4" t="s">
+        <v>1687</v>
+      </c>
+      <c r="Y187" s="5">
+        <v>145</v>
+      </c>
+      <c r="Z187" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="AA187" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="188" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="189" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="190" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22836,8 +23081,12 @@
     <hyperlink ref="D185" r:id="rId23"/>
     <hyperlink ref="C185" r:id="rId24"/>
     <hyperlink ref="E185" r:id="rId25"/>
+    <hyperlink ref="D186" r:id="rId26"/>
+    <hyperlink ref="E186" r:id="rId27"/>
+    <hyperlink ref="C186" r:id="rId28"/>
+    <hyperlink ref="G186" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="1689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1705">
   <si>
     <t>Facebook</t>
   </si>
@@ -6568,110 +6568,273 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>https://play.google.com/store/apps/details?id=com.dreamplay.hiddenheroes.google&amp;fbclid=IwY2xjawMIIqZleHRuA2FlbQIxMABicmlkETFkZXV4UHJOSGFrcm92WWVYAR4-fZWlGr15cqSHFRjjaQwTW4OE4HDAfdBZ5LKH4DG9IgD3Tidgy-Udr-Yk3w_aem_evKrdZdXYqQCCS1J3i2qBg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/hk/app/%E6%9C%AA%E9%91%91%E5%AE%9A%E5%8B%87%E8%80%85%E5%9C%98-%E9%81%8B%E6%B0%A3%E5%9E%8B%E6%94%BE%E7%BD%AErpg/id6744206189</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61577386190686</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/B.php?bsn=83087</t>
+  </si>
+  <si>
+    <t>https://soul.staroio.com/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/SpiritTaleSociety</t>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E6%88%B0%E9%9D%88%E7%95%B0%E8%81%9E%E7%A4%BE/id6745178365</t>
+  </si>
+  <si>
+    <t>13000翡翠</t>
+  </si>
+  <si>
+    <t>3450翡翠</t>
+  </si>
+  <si>
+    <t>600翡翠</t>
+  </si>
+  <si>
+    <t>難度通行證</t>
+  </si>
+  <si>
+    <t>勇者等級通行證</t>
+  </si>
+  <si>
+    <t>99.99禮包</t>
+  </si>
+  <si>
+    <t>49.99禮包</t>
+  </si>
+  <si>
+    <t>29.99禮包</t>
+  </si>
+  <si>
+    <t>19.99禮包</t>
+  </si>
+  <si>
+    <t>14.99禮包</t>
+  </si>
+  <si>
+    <t>12.99禮包</t>
+  </si>
+  <si>
+    <t>9.99禮包</t>
+  </si>
+  <si>
+    <t>4.99禮包</t>
+  </si>
+  <si>
+    <t>0.99禮包</t>
+  </si>
+  <si>
+    <t>見習骷髏王</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apps.apple.com/tw/app/%E8%A6%8B%E7%BF%92%E9%AA%B7%E9%AB%8F%E7%8E%8B/id6747066550</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/KLWOfficial</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://klw.togaado.com/#/</t>
+  </si>
+  <si>
+    <t>https://forum.gamer.com.tw/B.php?bsn=83350</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2490禮包</t>
+  </si>
+  <si>
+    <t>2290禮包</t>
+  </si>
+  <si>
+    <t>1690禮包</t>
+  </si>
+  <si>
+    <t>1490禮包</t>
+  </si>
+  <si>
+    <t>1190禮包</t>
+  </si>
+  <si>
+    <t>670禮包</t>
+  </si>
+  <si>
+    <t>330禮包</t>
+  </si>
+  <si>
+    <t>230禮包</t>
+  </si>
+  <si>
+    <t>170禮包</t>
+  </si>
+  <si>
+    <t>33禮包</t>
+  </si>
+  <si>
+    <r>
+      <t>《未鑑定勇者團》是一款像素風放置型 RPG，帶您進入懷舊與冒險的奇幻世界。其核心特色在於獨特的「未鑑定」系統，玩家將招募職業、潛力皆未知的勇者，透過細心培養和鑑定，發掘最強大的隱藏英雄。遊戲玩法輕鬆，離線也能持續獲得收益，讓您無痛養成勇者隊伍。為了讓冒險之路更順暢，別忘了查找最新的</t>
+    </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
         <charset val="136"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>《未鑑定勇者團》是一款像素風格的放置型</t>
+      <t>禮包碼</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> RPG </t>
+      <t>，兌換豐富獎勵以快速提升戰力。若想取得更多優勢，也可考慮安全的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，輕鬆獲取稀有道具，打造無堅不摧的勇者團。立即加入，揭開所有勇者的神秘面紗，展開獨一無二的冒險！</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>《戰靈異聞社》是款都市怪談風卡牌放置手遊，帶您進入現代與靈異交織的世界。您將扮演「異聞社」社長，解決各種超自然事件。遊戲美術風格獨特，融合潮流與傳統，打造出百位各具特色的「戰靈」。玩家需策略性組合隊伍，利用戰靈羈絆與技能，挑戰詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌中也能享受卡牌養成樂趣。官方常發放福利，記得關注社群領取最新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
         <charset val="136"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>手遊，帶您進入一個充滿懷舊與冒險的奇幻世界。遊戲核心特色在於其獨特的「未鑑定」系統，玩家將招募各種職業的勇者，他們的能力與潛力都是未知的，需要透過您的細心培養和鑑定，才能發掘出最強大的隱藏英雄。遊戲玩法輕鬆，即使離線也能持續獲得收益，讓您輕鬆養成您的勇者隊伍。為了讓您的冒險之路更加順暢，別忘了隨時查找最新的禮包碼，兌換豐富的虛寶獎勵，快速提升戰力。若想在遊戲中取得更多優勢，也可以考慮使用安全的代儲值服務，輕鬆獲取鑽石與各種稀有道具，打造無堅不摧的傳奇勇者團。立即加入，揭開所有未鑑定勇者的神秘面紗，展開一場獨一無二的冒險旅程！</t>
+      <t>禮包碼</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《戰靈異聞社》是一款都市怪談風格的卡牌放置手遊。遊戲將您帶入一個現代與靈異交織的世界，您將扮演「異聞社」的社長，專門解決各種超自然事件。遊戲美術風格獨特，融合了潮流與傳統元素，打造出百位以上各具特色的「戰靈」。玩家需要策略性地組合隊伍，利用戰靈之間的羈絆與技能，挑戰各種詭譎的都市傳說。遊戲主打輕鬆護肝的放置玩法，讓您在忙碌之餘也能享受卡牌養成的樂趣。官方經常發放福利，記得要關注社群平台領取最新的禮包碼，強化您的戰靈隊伍。對於追求極致遊戲體驗的玩家，尋找可靠的代儲值管道能幫助您更快地收集心儀角色，解鎖更強大的力量，帶領您的異聞社，揭開所有神秘事件背後的真相。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://play.google.com/store/apps/details?id=com.dreamplay.hiddenheroes.google&amp;fbclid=IwY2xjawMIIqZleHRuA2FlbQIxMABicmlkETFkZXV4UHJOSGFrcm92WWVYAR4-fZWlGr15cqSHFRjjaQwTW4OE4HDAfdBZ5LKH4DG9IgD3Tidgy-Udr-Yk3w_aem_evKrdZdXYqQCCS1J3i2qBg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apps.apple.com/hk/app/%E6%9C%AA%E9%91%91%E5%AE%9A%E5%8B%87%E8%80%85%E5%9C%98-%E9%81%8B%E6%B0%A3%E5%9E%8B%E6%94%BE%E7%BD%AErpg/id6744206189</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/profile.php?id=61577386190686</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://forum.gamer.com.tw/B.php?bsn=83087</t>
-  </si>
-  <si>
-    <t>https://soul.staroio.com/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/SpiritTaleSociety</t>
-  </si>
-  <si>
-    <t>https://apps.apple.com/tw/app/%E6%88%B0%E9%9D%88%E7%95%B0%E8%81%9E%E7%A4%BE/id6745178365</t>
-  </si>
-  <si>
-    <t>13000翡翠</t>
-  </si>
-  <si>
-    <t>3450翡翠</t>
-  </si>
-  <si>
-    <t>600翡翠</t>
-  </si>
-  <si>
-    <t>難度通行證</t>
-  </si>
-  <si>
-    <t>勇者等級通行證</t>
-  </si>
-  <si>
-    <t>99.99禮包</t>
-  </si>
-  <si>
-    <t>49.99禮包</t>
-  </si>
-  <si>
-    <t>29.99禮包</t>
-  </si>
-  <si>
-    <t>19.99禮包</t>
-  </si>
-  <si>
-    <t>14.99禮包</t>
-  </si>
-  <si>
-    <t>12.99禮包</t>
-  </si>
-  <si>
-    <t>9.99禮包</t>
-  </si>
-  <si>
-    <t>4.99禮包</t>
-  </si>
-  <si>
-    <t>0.99禮包</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，強化您的隊伍。為追求極致體驗，尋找可靠的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管道能助您更快收集角色、解鎖強大力量，帶領異聞社揭開所有事件的真相。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>《見習骷髏王》是一款別出心裁的放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演從墳墓甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。為加速霸業，別忘了尋找社群發布的最新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>禮包碼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，兌換關鍵資源讓軍團更壯大。若想在初期取得壓倒性優勢，可考慮使用便利的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代儲值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服務，確保您能輕鬆碾壓前來挑戰的勇者。立即加入，帶領您的骷髏大軍，征服整個世界！</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6754,6 +6917,15 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="1"/>
@@ -18145,7 +18317,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H187" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H188" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -21093,7 +21265,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F187" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F188" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -22875,13 +23047,13 @@
         <v>1664</v>
       </c>
       <c r="C186" s="37" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="D186" s="36" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="E186" s="36" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="F186" s="11" t="str">
         <f t="shared" si="6"/>
@@ -22894,35 +23066,35 @@
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=未鑑定勇者團</v>
       </c>
-      <c r="I186" s="24" t="s">
-        <v>1666</v>
+      <c r="I186" t="s">
+        <v>1702</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="K186" s="5">
         <v>2355</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="M186" s="5">
         <v>937</v>
       </c>
       <c r="N186" s="4" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="O186" s="5">
         <v>232</v>
       </c>
       <c r="P186" s="4" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="Q186" s="5">
         <v>176</v>
       </c>
       <c r="R186" s="4" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="S186" s="5">
         <v>102</v>
@@ -22933,84 +23105,177 @@
         <v>1665</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="D187" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>1672</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>1674</v>
       </c>
       <c r="F187" s="11" t="str">
         <f t="shared" si="6"/>
         <v>gift-codes.html?game=戰靈異聞社</v>
       </c>
       <c r="G187" s="36" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="H187" s="13" t="str">
         <f t="shared" si="5"/>
         <v>https://www.ssbuy.tw/game-detail.html?game=戰靈異聞社</v>
       </c>
-      <c r="I187" s="34" t="s">
-        <v>1667</v>
+      <c r="I187" t="s">
+        <v>1703</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="K187" s="5">
         <v>2555</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="M187" s="5">
         <v>1331</v>
       </c>
       <c r="N187" s="4" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="O187" s="5">
         <v>788</v>
       </c>
       <c r="P187" s="4" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="Q187" s="5">
         <v>535</v>
       </c>
       <c r="R187" s="4" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="S187" s="5">
         <v>391</v>
       </c>
       <c r="T187" s="4" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="U187" s="5">
         <v>343</v>
       </c>
       <c r="V187" s="4" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="W187" s="5">
         <v>264</v>
       </c>
       <c r="X187" s="4" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="Y187" s="5">
         <v>145</v>
       </c>
       <c r="Z187" s="4" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="AA187" s="5">
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="35" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C188" s="37" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D188" s="36" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E188" s="36" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F188" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=見習骷髏王</v>
+      </c>
+      <c r="G188" s="36" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H188" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=見習骷髏王</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J188" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="K188" s="5">
+        <v>1961</v>
+      </c>
+      <c r="L188" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="M188" s="5">
+        <v>1804</v>
+      </c>
+      <c r="N188" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="O188" s="5">
+        <v>1331</v>
+      </c>
+      <c r="P188" s="4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="Q188" s="5">
+        <v>1174</v>
+      </c>
+      <c r="R188" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="S188" s="5">
+        <v>937</v>
+      </c>
+      <c r="T188" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U188" s="5">
+        <v>780</v>
+      </c>
+      <c r="V188" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="W188" s="5">
+        <v>535</v>
+      </c>
+      <c r="X188" s="4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="Y188" s="5">
+        <v>264</v>
+      </c>
+      <c r="Z188" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="AA188" s="5">
+        <v>184</v>
+      </c>
+      <c r="AB188" s="4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AC188" s="5">
+        <v>145</v>
+      </c>
+      <c r="AD188" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AE188" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="189" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="190" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="191" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -23085,8 +23350,11 @@
     <hyperlink ref="E186" r:id="rId27"/>
     <hyperlink ref="C186" r:id="rId28"/>
     <hyperlink ref="G186" r:id="rId29"/>
+    <hyperlink ref="E188" r:id="rId30"/>
+    <hyperlink ref="C188" r:id="rId31"/>
+    <hyperlink ref="G188" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
 </worksheet>
 </file>
--- a/games.xlsx
+++ b/games.xlsx
@@ -6782,7 +6782,7 @@
   </si>
   <si>
     <r>
-      <t>《見習骷髏王》是一款別出心裁的放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演從墳墓甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。為加速霸業，別忘了尋找社群發布的最新</t>
+      <t>《見習骷髏王》是一款放置養成 RPG，讓您體驗「骨」起勇氣做反派的獨特樂趣！您將扮演甦醒的見習骷髏王，目標是建立自己的不死軍團。遊戲採用可愛搞怪的畫風，顛覆骷髏的恐怖印象。核心玩法圍繞放置與合成，透過擊敗英雄、召喚魔物夥伴，並合成更強大的怪物來擴充軍勢。離線也能累積資源，上線即享戰力飆升快感。別忘了尋找社群發布的最新</t>
     </r>
     <r>
       <rPr>
@@ -6826,8 +6826,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>服務，確保您能輕鬆碾壓前來挑戰的勇者。立即加入，帶領您的骷髏大軍，征服整個世界！</t>
+      <t>服務，確保您能輕鬆碾壓前來挑戰的勇者。帶領您的骷髏大軍，征服整個世界！</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/games.xlsx
+++ b/games.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1709">
   <si>
     <t>Facebook</t>
   </si>
@@ -6830,12 +6830,151 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.facebook.com/allstarws</t>
+  </si>
+  <si>
+    <t>全明星無雙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>https://apps.apple.com/app/id6748193496</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="10"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>《全明星無雙》是一款集結超人氣動漫角色的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>動作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>盜版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>手遊，打造夢幻的跨次元戰場。遊戲採用次世代技術，呈現華麗戰鬥畫面與流暢連招，帶來前所未有的打擊快感。您可以收集悟空、魯夫、炭治郎等英雄，組建最強隊伍。玩法豐富，有沉浸式主線劇情、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PVP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>競技場與團隊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Raid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>副本。為了幫助玩家快速成長，官方經常發放最新的禮包碼，讓您輕鬆獲得稀有道具。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSbuy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>也提供便利安全的代儲值服務，確保您消費物超所值，在稱霸全明星的道路上暢行無阻！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6928,6 +7067,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
@@ -18318,7 +18466,7 @@
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13" t="str">
-        <f t="shared" ref="H131:H188" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
+        <f t="shared" ref="H131:H189" si="5">"https://www.ssbuy.tw/game-detail.html?game="&amp;A131</f>
         <v>https://www.ssbuy.tw/game-detail.html?game=緋石之心</v>
       </c>
       <c r="I131" s="22" t="s">
@@ -21266,7 +21414,7 @@
         <v>1452</v>
       </c>
       <c r="F162" s="11" t="str">
-        <f t="shared" ref="F162:F188" si="6">"gift-codes.html?game=" &amp; A162</f>
+        <f t="shared" ref="F162:F189" si="6">"gift-codes.html?game=" &amp; A162</f>
         <v>gift-codes.html?game=小兵立大功</v>
       </c>
       <c r="H162" s="13" t="str">
@@ -23277,7 +23425,82 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:35" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="35" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E189" s="36" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F189" s="11" t="str">
+        <f t="shared" si="6"/>
+        <v>gift-codes.html?game=全明星無雙</v>
+      </c>
+      <c r="G189" s="36" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H189" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>https://www.ssbuy.tw/game-detail.html?game=全明星無雙</v>
+      </c>
+      <c r="I189" s="24" t="s">
+        <v>1708</v>
+      </c>
+      <c r="J189" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K189" s="5">
+        <v>2555</v>
+      </c>
+      <c r="L189" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M189" s="5">
+        <v>1331</v>
+      </c>
+      <c r="N189" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O189" s="5">
+        <v>780</v>
+      </c>
+      <c r="P189" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q189" s="5">
+        <v>535</v>
+      </c>
+      <c r="R189" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="S189" s="5">
+        <v>391</v>
+      </c>
+      <c r="T189" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U189" s="5">
+        <v>264</v>
+      </c>
+      <c r="V189" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="W189" s="5">
+        <v>145</v>
+      </c>
+      <c r="X189" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y189" s="5">
+        <v>28</v>
+      </c>
+    </row>
     <row r="190" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="191" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="192" spans="1:35" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -23354,8 +23577,10 @@
     <hyperlink ref="E188" r:id="rId30"/>
     <hyperlink ref="C188" r:id="rId31"/>
     <hyperlink ref="G188" r:id="rId32"/>
+    <hyperlink ref="G189" r:id="rId33"/>
+    <hyperlink ref="E189" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>